--- a/content/dblogr/usa_crime/usa_crime_data.xlsx
+++ b/content/dblogr/usa_crime/usa_crime_data.xlsx
@@ -4,29 +4,30 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Murders" sheetId="3" r:id="rId1"/>
-    <sheet name="Race1" sheetId="1" r:id="rId2"/>
-    <sheet name="Race2" sheetId="2" r:id="rId3"/>
-    <sheet name="18tbl43a" sheetId="4" r:id="rId4"/>
-    <sheet name="18tbl43c" sheetId="5" r:id="rId5"/>
-    <sheet name="18tbl43b" sheetId="6" r:id="rId6"/>
-    <sheet name="18tbl01" sheetId="7" r:id="rId7"/>
+    <sheet name="Race0" sheetId="8" r:id="rId2"/>
+    <sheet name="Race1" sheetId="1" r:id="rId3"/>
+    <sheet name="Race2" sheetId="2" r:id="rId4"/>
+    <sheet name="18tbl43a" sheetId="4" r:id="rId5"/>
+    <sheet name="18tbl43c" sheetId="5" r:id="rId6"/>
+    <sheet name="18tbl43b" sheetId="6" r:id="rId7"/>
+    <sheet name="18tbl01" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'18tbl01'!$A$1:$V$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'18tbl43a'!$A$1:$S$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'18tbl43b'!$A$1:$S$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'18tbl43c'!$A$1:$S$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'18tbl01'!$A$1:$V$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'18tbl43a'!$A$1:$S$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'18tbl43b'!$A$1:$S$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'18tbl43c'!$A$1:$S$42</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="139">
   <si>
     <t>Victim</t>
   </si>
@@ -760,6 +761,9 @@
   </si>
   <si>
     <t>Table 1</t>
+  </si>
+  <si>
+    <t>ViolentIncidents</t>
   </si>
 </sst>
 </file>
@@ -1448,21 +1452,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1488,12 +1477,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="167" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1599,6 +1584,25 @@
     <xf numFmtId="167" fontId="28" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="28" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1 2" xfId="4"/>
@@ -2333,6 +2337,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>3581360</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>563940</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>734410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>182230</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2616,7 +2670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2780,7 +2834,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2808,30 +2862,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
     </row>
     <row r="2" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="39" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="27"/>
@@ -2840,98 +2894,98 @@
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
     </row>
     <row r="3" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="36" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
     </row>
     <row r="5" spans="1:19" s="34" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="38" t="s">
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="36" t="s">
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="38" t="s">
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
+      <c r="R5" s="107"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" spans="1:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="106"/>
+      <c r="B6" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="36" t="s">
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="108"/>
     </row>
     <row r="7" spans="1:19" s="28" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
@@ -4924,7 +4978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4952,115 +5006,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
     </row>
     <row r="2" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="48" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="36" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
     </row>
     <row r="5" spans="1:19" s="34" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="38" t="s">
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="36" t="s">
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="38" t="s">
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
+      <c r="R5" s="107"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" spans="1:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="111"/>
+      <c r="B6" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="36" t="s">
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="108"/>
     </row>
     <row r="7" spans="1:19" s="28" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="47" t="s">
         <v>75</v>
       </c>
       <c r="B7" s="30" t="s">
@@ -5184,16 +5238,16 @@
       <c r="B9" s="6">
         <v>8264</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="46">
         <v>3673</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="46">
         <v>4377</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="46">
         <v>99</v>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="46">
         <v>91</v>
       </c>
       <c r="G9" s="20">
@@ -5243,16 +5297,16 @@
       <c r="B10" s="6">
         <v>15706</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="46">
         <v>10677</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="46">
         <v>4492</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="46">
         <v>234</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="46">
         <v>259</v>
       </c>
       <c r="G10" s="20">
@@ -5302,16 +5356,16 @@
       <c r="B11" s="6">
         <v>53707</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="46">
         <v>24602</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="46">
         <v>27789</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="46">
         <v>604</v>
       </c>
-      <c r="F11" s="51">
+      <c r="F11" s="46">
         <v>516</v>
       </c>
       <c r="G11" s="20">
@@ -5361,16 +5415,16 @@
       <c r="B12" s="6">
         <v>277097</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="46">
         <v>172900</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="46">
         <v>91786</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="46">
         <v>6368</v>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="46">
         <v>4810</v>
       </c>
       <c r="G12" s="20">
@@ -5420,16 +5474,16 @@
       <c r="B13" s="6">
         <v>117843</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="46">
         <v>82398</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="46">
         <v>32588</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="46">
         <v>1310</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="46">
         <v>1267</v>
       </c>
       <c r="G13" s="20">
@@ -5479,16 +5533,16 @@
       <c r="B14" s="6">
         <v>600408</v>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="46">
         <v>409000</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="46">
         <v>173055</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="46">
         <v>10844</v>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="46">
         <v>6323</v>
       </c>
       <c r="G14" s="20">
@@ -5538,16 +5592,16 @@
       <c r="B15" s="6">
         <v>57913</v>
       </c>
-      <c r="C15" s="51">
+      <c r="C15" s="46">
         <v>39536</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="46">
         <v>16525</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="46">
         <v>939</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="46">
         <v>734</v>
       </c>
       <c r="G15" s="20">
@@ -5597,16 +5651,16 @@
       <c r="B16" s="6">
         <v>5608</v>
       </c>
-      <c r="C16" s="51">
+      <c r="C16" s="46">
         <v>4031</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="46">
         <v>1356</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="46">
         <v>111</v>
       </c>
-      <c r="F16" s="51">
+      <c r="F16" s="46">
         <v>84</v>
       </c>
       <c r="G16" s="20">
@@ -5774,16 +5828,16 @@
       <c r="B19" s="6">
         <v>701782</v>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="46">
         <v>457339</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="46">
         <v>218686</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="46">
         <v>14165</v>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="46">
         <v>9516</v>
       </c>
       <c r="G19" s="20">
@@ -5833,16 +5887,16 @@
       <c r="B20" s="6">
         <v>36945</v>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="46">
         <v>24695</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="46">
         <v>11323</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="46">
         <v>329</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="46">
         <v>537</v>
       </c>
       <c r="G20" s="20">
@@ -5892,16 +5946,16 @@
       <c r="B21" s="6">
         <v>86111</v>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="46">
         <v>57125</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="46">
         <v>26443</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="46">
         <v>1352</v>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="46">
         <v>1052</v>
       </c>
       <c r="G21" s="20">
@@ -5951,16 +6005,16 @@
       <c r="B22" s="6">
         <v>10739</v>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="46">
         <v>6694</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="46">
         <v>3767</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="46">
         <v>118</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="46">
         <v>147</v>
       </c>
       <c r="G22" s="20">
@@ -6010,16 +6064,16 @@
       <c r="B23" s="6">
         <v>62938</v>
       </c>
-      <c r="C23" s="51">
+      <c r="C23" s="46">
         <v>41581</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="46">
         <v>19538</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="46">
         <v>805</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="46">
         <v>724</v>
       </c>
       <c r="G23" s="20">
@@ -6069,16 +6123,16 @@
       <c r="B24" s="6">
         <v>112041</v>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="46">
         <v>75758</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="46">
         <v>32275</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="46">
         <v>2453</v>
       </c>
-      <c r="F24" s="51">
+      <c r="F24" s="46">
         <v>1355</v>
       </c>
       <c r="G24" s="20">
@@ -6128,16 +6182,16 @@
       <c r="B25" s="6">
         <v>113492</v>
       </c>
-      <c r="C25" s="51">
+      <c r="C25" s="46">
         <v>61773</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="46">
         <v>49214</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="46">
         <v>960</v>
       </c>
-      <c r="F25" s="51">
+      <c r="F25" s="46">
         <v>1206</v>
       </c>
       <c r="G25" s="20">
@@ -6187,16 +6241,16 @@
       <c r="B26" s="6">
         <v>23303</v>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="46">
         <v>12810</v>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="46">
         <v>9034</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="46">
         <v>92</v>
       </c>
-      <c r="F26" s="51">
+      <c r="F26" s="46">
         <v>1307</v>
       </c>
       <c r="G26" s="20">
@@ -6246,16 +6300,16 @@
       <c r="B27" s="6">
         <v>29572</v>
       </c>
-      <c r="C27" s="51">
+      <c r="C27" s="46">
         <v>21276</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="46">
         <v>7042</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="46">
         <v>526</v>
       </c>
-      <c r="F27" s="51">
+      <c r="F27" s="46">
         <v>667</v>
       </c>
       <c r="G27" s="20">
@@ -6305,16 +6359,16 @@
       <c r="B28" s="6">
         <v>1167082</v>
       </c>
-      <c r="C28" s="51">
+      <c r="C28" s="46">
         <v>821984</v>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="46">
         <v>317809</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="46">
         <v>12791</v>
       </c>
-      <c r="F28" s="51">
+      <c r="F28" s="46">
         <v>12443</v>
       </c>
       <c r="G28" s="20">
@@ -6364,16 +6418,16 @@
       <c r="B29" s="6">
         <v>2331</v>
       </c>
-      <c r="C29" s="51">
+      <c r="C29" s="46">
         <v>970</v>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="46">
         <v>1095</v>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="46">
         <v>10</v>
       </c>
-      <c r="F29" s="51">
+      <c r="F29" s="46">
         <v>205</v>
       </c>
       <c r="G29" s="20">
@@ -6423,16 +6477,16 @@
       <c r="B30" s="6">
         <v>61910</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="46">
         <v>41697</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="46">
         <v>17957</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="46">
         <v>1714</v>
       </c>
-      <c r="F30" s="51">
+      <c r="F30" s="46">
         <v>492</v>
       </c>
       <c r="G30" s="20">
@@ -6482,16 +6536,16 @@
       <c r="B31" s="6">
         <v>732646</v>
       </c>
-      <c r="C31" s="51">
+      <c r="C31" s="46">
         <v>594407</v>
       </c>
-      <c r="D31" s="51">
+      <c r="D31" s="46">
         <v>108425</v>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="46">
         <v>13017</v>
       </c>
-      <c r="F31" s="51">
+      <c r="F31" s="46">
         <v>14259</v>
       </c>
       <c r="G31" s="20">
@@ -6541,16 +6595,16 @@
       <c r="B32" s="6">
         <v>108923</v>
       </c>
-      <c r="C32" s="51">
+      <c r="C32" s="46">
         <v>83666</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="46">
         <v>17483</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="46">
         <v>6014</v>
       </c>
-      <c r="F32" s="51">
+      <c r="F32" s="46">
         <v>1632</v>
       </c>
       <c r="G32" s="20">
@@ -6600,16 +6654,16 @@
       <c r="B33" s="6">
         <v>249011</v>
       </c>
-      <c r="C33" s="51">
+      <c r="C33" s="46">
         <v>191053</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="46">
         <v>37465</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="46">
         <v>17274</v>
       </c>
-      <c r="F33" s="51">
+      <c r="F33" s="46">
         <v>2793</v>
       </c>
       <c r="G33" s="20">
@@ -6659,16 +6713,16 @@
       <c r="B34" s="6">
         <v>205095</v>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="46">
         <v>134516</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="46">
         <v>59775</v>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="46">
         <v>8903</v>
       </c>
-      <c r="F34" s="51">
+      <c r="F34" s="46">
         <v>1640</v>
       </c>
       <c r="G34" s="20">
@@ -6718,16 +6772,16 @@
       <c r="B35" s="6">
         <v>17523</v>
       </c>
-      <c r="C35" s="51">
+      <c r="C35" s="46">
         <v>12558</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="46">
         <v>4212</v>
       </c>
-      <c r="E35" s="51">
+      <c r="E35" s="46">
         <v>474</v>
       </c>
-      <c r="F35" s="51">
+      <c r="F35" s="46">
         <v>257</v>
       </c>
       <c r="G35" s="20">
@@ -6777,16 +6831,16 @@
       <c r="B36" s="6">
         <v>2309275</v>
       </c>
-      <c r="C36" s="51">
+      <c r="C36" s="46">
         <v>1596694</v>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="46">
         <v>632157</v>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="46">
         <v>52517</v>
       </c>
-      <c r="F36" s="51">
+      <c r="F36" s="46">
         <v>22580</v>
       </c>
       <c r="G36" s="20">
@@ -6836,16 +6890,16 @@
       <c r="B37" s="6">
         <v>393</v>
       </c>
-      <c r="C37" s="51">
+      <c r="C37" s="46">
         <v>214</v>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="46">
         <v>117</v>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="46">
         <v>61</v>
       </c>
-      <c r="F37" s="51">
+      <c r="F37" s="46">
         <v>1</v>
       </c>
       <c r="G37" s="20">
@@ -6889,61 +6943,61 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="50" t="s">
+      <c r="A38" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="49" t="s">
+      <c r="B38" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="48" t="s">
+      <c r="C38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="E38" s="48" t="s">
+      <c r="E38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="F38" s="48" t="s">
+      <c r="F38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="G38" s="48" t="s">
+      <c r="G38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="H38" s="48" t="s">
+      <c r="H38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="I38" s="48" t="s">
+      <c r="I38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="J38" s="48" t="s">
+      <c r="J38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="K38" s="48" t="s">
+      <c r="K38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="L38" s="48" t="s">
+      <c r="L38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="M38" s="48" t="s">
+      <c r="M38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="N38" s="48" t="s">
+      <c r="N38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="O38" s="48" t="s">
+      <c r="O38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="P38" s="48" t="s">
+      <c r="P38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="Q38" s="48" t="s">
+      <c r="Q38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="R38" s="48" t="s">
+      <c r="R38" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="S38" s="48" t="s">
+      <c r="S38" s="43" t="s">
         <v>83</v>
       </c>
     </row>
@@ -7001,10 +7055,10 @@
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
-      <c r="N41" s="47"/>
-      <c r="O41" s="47"/>
-      <c r="P41" s="47"/>
-      <c r="Q41" s="47"/>
+      <c r="N41" s="42"/>
+      <c r="O41" s="42"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
     </row>
     <row r="42" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
@@ -7040,7 +7094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7066,35 +7120,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
     </row>
     <row r="2" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="48" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="36" t="s">
         <v>85</v>
       </c>
       <c r="E3" s="34" t="s">
@@ -7102,79 +7156,79 @@
       </c>
     </row>
     <row r="4" spans="1:19" s="34" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
     </row>
     <row r="5" spans="1:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="38" t="s">
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="36" t="s">
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="109" t="s">
         <v>89</v>
       </c>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="38" t="s">
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
+      <c r="R5" s="107"/>
+      <c r="S5" s="107"/>
     </row>
     <row r="6" spans="1:19" s="34" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="113"/>
+      <c r="B6" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="36" t="s">
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="108"/>
     </row>
     <row r="7" spans="1:19" s="28" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
@@ -7301,16 +7355,16 @@
       <c r="B9" s="6">
         <v>693</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="46">
         <v>280</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="46">
         <v>401</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="46">
         <v>6</v>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="46">
         <v>3</v>
       </c>
       <c r="G9" s="20">
@@ -7360,16 +7414,16 @@
       <c r="B10" s="6">
         <v>3070</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="46">
         <v>2117</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="46">
         <v>884</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="46">
         <v>33</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="46">
         <v>30</v>
       </c>
       <c r="G10" s="20">
@@ -7419,16 +7473,16 @@
       <c r="B11" s="6">
         <v>13082</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="46">
         <v>4423</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="46">
         <v>8398</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="46">
         <v>72</v>
       </c>
-      <c r="F11" s="51">
+      <c r="F11" s="46">
         <v>125</v>
       </c>
       <c r="G11" s="20">
@@ -7478,16 +7532,16 @@
       <c r="B12" s="6">
         <v>20943</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="46">
         <v>11627</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="46">
         <v>8607</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="46">
         <v>368</v>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="46">
         <v>268</v>
       </c>
       <c r="G12" s="20">
@@ -7537,16 +7591,16 @@
       <c r="B13" s="6">
         <v>16699</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="46">
         <v>9183</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="46">
         <v>7029</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="46">
         <v>280</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="46">
         <v>155</v>
       </c>
       <c r="G13" s="20">
@@ -7596,16 +7650,16 @@
       <c r="B14" s="6">
         <v>69575</v>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="46">
         <v>39193</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="46">
         <v>28031</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="46">
         <v>1143</v>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="46">
         <v>1001</v>
       </c>
       <c r="G14" s="20">
@@ -7655,16 +7709,16 @@
       <c r="B15" s="6">
         <v>11089</v>
       </c>
-      <c r="C15" s="51">
+      <c r="C15" s="46">
         <v>4976</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="46">
         <v>5780</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="46">
         <v>212</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="46">
         <v>84</v>
       </c>
       <c r="G15" s="20">
@@ -7714,16 +7768,16 @@
       <c r="B16" s="6">
         <v>1338</v>
       </c>
-      <c r="C16" s="51">
+      <c r="C16" s="46">
         <v>907</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="46">
         <v>384</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="46">
         <v>26</v>
       </c>
-      <c r="F16" s="51">
+      <c r="F16" s="46">
         <v>17</v>
       </c>
       <c r="G16" s="20">
@@ -7891,16 +7945,16 @@
       <c r="B19" s="6">
         <v>93005</v>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="46">
         <v>54686</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="46">
         <v>35674</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="46">
         <v>1546</v>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="46">
         <v>832</v>
       </c>
       <c r="G19" s="20">
@@ -7950,16 +8004,16 @@
       <c r="B20" s="6">
         <v>779</v>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="46">
         <v>445</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="46">
         <v>314</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="46">
         <v>6</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="46">
         <v>11</v>
       </c>
       <c r="G20" s="20">
@@ -8009,16 +8063,16 @@
       <c r="B21" s="6">
         <v>3499</v>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="46">
         <v>1447</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="46">
         <v>1944</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="46">
         <v>67</v>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="46">
         <v>36</v>
       </c>
       <c r="G21" s="20">
@@ -8068,16 +8122,16 @@
       <c r="B22" s="6">
         <v>435</v>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="46">
         <v>229</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="46">
         <v>188</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="46">
         <v>4</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="46">
         <v>12</v>
       </c>
       <c r="G22" s="20">
@@ -8127,16 +8181,16 @@
       <c r="B23" s="6">
         <v>6936</v>
       </c>
-      <c r="C23" s="51">
+      <c r="C23" s="46">
         <v>2598</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="46">
         <v>4123</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="46">
         <v>76</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="46">
         <v>95</v>
       </c>
       <c r="G23" s="20">
@@ -8186,16 +8240,16 @@
       <c r="B24" s="6">
         <v>22753</v>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="46">
         <v>15418</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="46">
         <v>6612</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="46">
         <v>496</v>
       </c>
-      <c r="F24" s="51">
+      <c r="F24" s="46">
         <v>197</v>
       </c>
       <c r="G24" s="20">
@@ -8245,16 +8299,16 @@
       <c r="B25" s="6">
         <v>12840</v>
       </c>
-      <c r="C25" s="51">
+      <c r="C25" s="46">
         <v>6983</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="46">
         <v>5501</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="46">
         <v>134</v>
       </c>
-      <c r="F25" s="51">
+      <c r="F25" s="46">
         <v>184</v>
       </c>
       <c r="G25" s="20">
@@ -8304,16 +8358,16 @@
       <c r="B26" s="6">
         <v>199</v>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="46">
         <v>118</v>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="46">
         <v>75</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="46">
         <v>3</v>
       </c>
-      <c r="F26" s="51">
+      <c r="F26" s="46">
         <v>2</v>
       </c>
       <c r="G26" s="20">
@@ -8363,16 +8417,16 @@
       <c r="B27" s="6">
         <v>5585</v>
       </c>
-      <c r="C27" s="51">
+      <c r="C27" s="46">
         <v>4062</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="46">
         <v>1361</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="46">
         <v>61</v>
       </c>
-      <c r="F27" s="51">
+      <c r="F27" s="46">
         <v>84</v>
       </c>
       <c r="G27" s="20">
@@ -8422,16 +8476,16 @@
       <c r="B28" s="6">
         <v>67096</v>
       </c>
-      <c r="C28" s="51">
+      <c r="C28" s="46">
         <v>49311</v>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="46">
         <v>15304</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="46">
         <v>1357</v>
       </c>
-      <c r="F28" s="51">
+      <c r="F28" s="46">
         <v>902</v>
       </c>
       <c r="G28" s="20">
@@ -8481,16 +8535,16 @@
       <c r="B29" s="6">
         <v>134</v>
       </c>
-      <c r="C29" s="51">
+      <c r="C29" s="46">
         <v>30</v>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="46">
         <v>103</v>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="46">
         <v>1</v>
       </c>
-      <c r="F29" s="51">
+      <c r="F29" s="46">
         <v>0</v>
       </c>
       <c r="G29" s="20">
@@ -8540,16 +8594,16 @@
       <c r="B30" s="6">
         <v>2447</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="46">
         <v>1674</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="46">
         <v>573</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="46">
         <v>181</v>
       </c>
-      <c r="F30" s="51">
+      <c r="F30" s="46">
         <v>18</v>
       </c>
       <c r="G30" s="20">
@@ -8599,16 +8653,16 @@
       <c r="B31" s="6">
         <v>3998</v>
       </c>
-      <c r="C31" s="51">
+      <c r="C31" s="46">
         <v>3512</v>
       </c>
-      <c r="D31" s="51">
+      <c r="D31" s="46">
         <v>278</v>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="46">
         <v>133</v>
       </c>
-      <c r="F31" s="51">
+      <c r="F31" s="46">
         <v>64</v>
       </c>
       <c r="G31" s="20">
@@ -8658,16 +8712,16 @@
       <c r="B32" s="6">
         <v>19530</v>
       </c>
-      <c r="C32" s="51">
+      <c r="C32" s="46">
         <v>17021</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="46">
         <v>1260</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="46">
         <v>959</v>
       </c>
-      <c r="F32" s="51">
+      <c r="F32" s="46">
         <v>244</v>
       </c>
       <c r="G32" s="20">
@@ -8717,16 +8771,16 @@
       <c r="B33" s="6">
         <v>2479</v>
       </c>
-      <c r="C33" s="51">
+      <c r="C33" s="46">
         <v>1989</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="46">
         <v>316</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="46">
         <v>138</v>
       </c>
-      <c r="F33" s="51">
+      <c r="F33" s="46">
         <v>32</v>
       </c>
       <c r="G33" s="20">
@@ -8776,16 +8830,16 @@
       <c r="B34" s="6">
         <v>43621</v>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="46">
         <v>24017</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="46">
         <v>18417</v>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="46">
         <v>867</v>
       </c>
-      <c r="F34" s="51">
+      <c r="F34" s="46">
         <v>286</v>
       </c>
       <c r="G34" s="20">
@@ -8835,16 +8889,16 @@
       <c r="B35" s="6">
         <v>525</v>
       </c>
-      <c r="C35" s="51">
+      <c r="C35" s="46">
         <v>265</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="46">
         <v>246</v>
       </c>
-      <c r="E35" s="51">
+      <c r="E35" s="46">
         <v>8</v>
       </c>
-      <c r="F35" s="51">
+      <c r="F35" s="46">
         <v>4</v>
       </c>
       <c r="G35" s="20">
@@ -8894,16 +8948,16 @@
       <c r="B36" s="6">
         <v>104133</v>
       </c>
-      <c r="C36" s="51">
+      <c r="C36" s="46">
         <v>70131</v>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="46">
         <v>30929</v>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="46">
         <v>1893</v>
       </c>
-      <c r="F36" s="51">
+      <c r="F36" s="46">
         <v>970</v>
       </c>
       <c r="G36" s="20">
@@ -8953,16 +9007,16 @@
       <c r="B37" s="6">
         <v>39</v>
       </c>
-      <c r="C37" s="51">
+      <c r="C37" s="46">
         <v>23</v>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="46">
         <v>12</v>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="46">
         <v>4</v>
       </c>
-      <c r="F37" s="51">
+      <c r="F37" s="46">
         <v>0</v>
       </c>
       <c r="G37" s="20">
@@ -9012,16 +9066,16 @@
       <c r="B38" s="6">
         <v>16720</v>
       </c>
-      <c r="C38" s="51">
+      <c r="C38" s="46">
         <v>9362</v>
       </c>
-      <c r="D38" s="51">
+      <c r="D38" s="46">
         <v>6852</v>
       </c>
-      <c r="E38" s="51">
+      <c r="E38" s="46">
         <v>272</v>
       </c>
-      <c r="F38" s="51">
+      <c r="F38" s="46">
         <v>184</v>
       </c>
       <c r="G38" s="20">
@@ -9126,12 +9180,12 @@
       <c r="A42" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
-      <c r="L42" s="56"/>
-      <c r="M42" s="56"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
     </row>
     <row r="43" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
@@ -9163,1506 +9217,1506 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X41"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" style="59" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" style="61" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="61"/>
-    <col min="4" max="4" width="8.5703125" style="60" customWidth="1"/>
-    <col min="5" max="5" width="10" style="61" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="60" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="61" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="60" customWidth="1"/>
-    <col min="9" max="9" width="9" style="63" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" style="62" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" style="61" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="60"/>
-    <col min="13" max="13" width="9" style="61" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="60"/>
-    <col min="15" max="15" width="9" style="61" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" style="60" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" style="61" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" style="60" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" style="61" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="60" customWidth="1"/>
-    <col min="21" max="21" width="8.5703125" style="61" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="60" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="59"/>
+    <col min="1" max="1" width="7.28515625" style="50" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="52" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="52"/>
+    <col min="4" max="4" width="8.5703125" style="51" customWidth="1"/>
+    <col min="5" max="5" width="10" style="52" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="51" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="52" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="51" customWidth="1"/>
+    <col min="9" max="9" width="9" style="54" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" style="53" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" style="52" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="51"/>
+    <col min="13" max="13" width="9" style="52" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="51"/>
+    <col min="15" max="15" width="9" style="52" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" style="51" customWidth="1"/>
+    <col min="17" max="17" width="8.85546875" style="52" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" style="51" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" style="52" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="51" customWidth="1"/>
+    <col min="21" max="21" width="8.5703125" style="52" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" style="51" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="113" t="s">
+    <row r="1" spans="1:24" s="91" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="110"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="110"/>
-      <c r="V1" s="109"/>
-    </row>
-    <row r="2" spans="1:24" s="105" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="108" t="s">
+      <c r="C1" s="101"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="100"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="100"/>
+    </row>
+    <row r="2" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="99" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-    </row>
-    <row r="3" spans="1:24" s="100" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="100" t="s">
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+    </row>
+    <row r="3" spans="1:24" s="91" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="91" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="102"/>
-      <c r="T3" s="101"/>
-      <c r="U3" s="102"/>
-      <c r="V3" s="101"/>
-    </row>
-    <row r="4" spans="1:24" s="94" customFormat="1" ht="49.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="96" t="s">
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="92"/>
+    </row>
+    <row r="4" spans="1:24" s="85" customFormat="1" ht="49.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="87" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="88" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="95" t="s">
+      <c r="D4" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="E4" s="96" t="s">
+      <c r="E4" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="86" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="99" t="s">
+      <c r="G4" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="H4" s="98" t="s">
+      <c r="H4" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="I4" s="99" t="s">
+      <c r="I4" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="J4" s="98" t="s">
+      <c r="J4" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="K4" s="96" t="s">
+      <c r="K4" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="95" t="s">
+      <c r="L4" s="86" t="s">
         <v>124</v>
       </c>
-      <c r="M4" s="96" t="s">
+      <c r="M4" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="N4" s="95" t="s">
+      <c r="N4" s="86" t="s">
         <v>122</v>
       </c>
-      <c r="O4" s="97" t="s">
+      <c r="O4" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="P4" s="95" t="s">
+      <c r="P4" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="Q4" s="96" t="s">
+      <c r="Q4" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="R4" s="95" t="s">
+      <c r="R4" s="86" t="s">
         <v>119</v>
       </c>
-      <c r="S4" s="96" t="s">
+      <c r="S4" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="T4" s="95" t="s">
+      <c r="T4" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="U4" s="96" t="s">
+      <c r="U4" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="V4" s="95" t="s">
+      <c r="V4" s="86" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A5" s="89">
+      <c r="A5" s="80">
         <v>1999</v>
       </c>
-      <c r="B5" s="87">
+      <c r="B5" s="78">
         <v>272690813</v>
       </c>
-      <c r="C5" s="87">
+      <c r="C5" s="78">
         <v>1426044</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="76">
         <v>523</v>
       </c>
-      <c r="E5" s="87">
+      <c r="E5" s="78">
         <v>15522</v>
       </c>
-      <c r="F5" s="85">
+      <c r="F5" s="76">
         <v>5.7</v>
       </c>
-      <c r="G5" s="87"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="92">
+      <c r="G5" s="78"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="83">
         <v>89411</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="79">
         <v>32.799999999999997</v>
       </c>
-      <c r="K5" s="87">
+      <c r="K5" s="78">
         <v>409371</v>
       </c>
-      <c r="L5" s="85">
+      <c r="L5" s="76">
         <v>150.1</v>
       </c>
-      <c r="M5" s="87">
+      <c r="M5" s="78">
         <v>911740</v>
       </c>
-      <c r="N5" s="85">
+      <c r="N5" s="76">
         <v>334.3</v>
       </c>
-      <c r="O5" s="87">
+      <c r="O5" s="78">
         <v>10208334</v>
       </c>
-      <c r="P5" s="86">
+      <c r="P5" s="77">
         <v>3743.6</v>
       </c>
-      <c r="Q5" s="87">
+      <c r="Q5" s="78">
         <v>2100739</v>
       </c>
-      <c r="R5" s="86">
+      <c r="R5" s="77">
         <v>770.4</v>
       </c>
-      <c r="S5" s="87">
+      <c r="S5" s="78">
         <v>6955520</v>
       </c>
-      <c r="T5" s="86">
+      <c r="T5" s="77">
         <v>2550.6999999999998</v>
       </c>
-      <c r="U5" s="87">
+      <c r="U5" s="78">
         <v>1152075</v>
       </c>
-      <c r="V5" s="85">
+      <c r="V5" s="76">
         <v>422.5</v>
       </c>
-      <c r="W5" s="59" t="s">
+      <c r="W5" s="50" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A6" s="89">
+      <c r="A6" s="80">
         <v>2000</v>
       </c>
-      <c r="B6" s="87">
+      <c r="B6" s="78">
         <v>281421906</v>
       </c>
-      <c r="C6" s="87">
+      <c r="C6" s="78">
         <v>1425486</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="76">
         <v>506.5</v>
       </c>
-      <c r="E6" s="87">
+      <c r="E6" s="78">
         <v>15586</v>
       </c>
-      <c r="F6" s="85">
+      <c r="F6" s="76">
         <v>5.5</v>
       </c>
-      <c r="G6" s="87"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="92">
+      <c r="G6" s="78"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="83">
         <v>90178</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="79">
         <v>32</v>
       </c>
-      <c r="K6" s="87">
+      <c r="K6" s="78">
         <v>408016</v>
       </c>
-      <c r="L6" s="85">
+      <c r="L6" s="76">
         <v>145</v>
       </c>
-      <c r="M6" s="87">
+      <c r="M6" s="78">
         <v>911706</v>
       </c>
-      <c r="N6" s="85">
+      <c r="N6" s="76">
         <v>324</v>
       </c>
-      <c r="O6" s="87">
+      <c r="O6" s="78">
         <v>10182584</v>
       </c>
-      <c r="P6" s="86">
+      <c r="P6" s="77">
         <v>3618.3</v>
       </c>
-      <c r="Q6" s="87">
+      <c r="Q6" s="78">
         <v>2050992</v>
       </c>
-      <c r="R6" s="86">
+      <c r="R6" s="77">
         <v>728.8</v>
       </c>
-      <c r="S6" s="87">
+      <c r="S6" s="78">
         <v>6971590</v>
       </c>
-      <c r="T6" s="86">
+      <c r="T6" s="77">
         <v>2477.3000000000002</v>
       </c>
-      <c r="U6" s="87">
+      <c r="U6" s="78">
         <v>1160002</v>
       </c>
-      <c r="V6" s="85">
+      <c r="V6" s="76">
         <v>412.2</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="87">
+      <c r="B7" s="78">
         <v>285317559</v>
       </c>
-      <c r="C7" s="87">
+      <c r="C7" s="78">
         <v>1439480</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="76">
         <v>504.5</v>
       </c>
-      <c r="E7" s="87">
+      <c r="E7" s="78">
         <v>16037</v>
       </c>
-      <c r="F7" s="85">
+      <c r="F7" s="76">
         <v>5.6</v>
       </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="92">
+      <c r="G7" s="78"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="83">
         <v>90863</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="79">
         <v>31.8</v>
       </c>
-      <c r="K7" s="87">
+      <c r="K7" s="78">
         <v>423557</v>
       </c>
-      <c r="L7" s="85">
+      <c r="L7" s="76">
         <v>148.5</v>
       </c>
-      <c r="M7" s="87">
+      <c r="M7" s="78">
         <v>909023</v>
       </c>
-      <c r="N7" s="85">
+      <c r="N7" s="76">
         <v>318.60000000000002</v>
       </c>
-      <c r="O7" s="87">
+      <c r="O7" s="78">
         <v>10437189</v>
       </c>
-      <c r="P7" s="86">
+      <c r="P7" s="77">
         <v>3658.1</v>
       </c>
-      <c r="Q7" s="87">
+      <c r="Q7" s="78">
         <v>2116531</v>
       </c>
-      <c r="R7" s="86">
+      <c r="R7" s="77">
         <v>741.8</v>
       </c>
-      <c r="S7" s="87">
+      <c r="S7" s="78">
         <v>7092267</v>
       </c>
-      <c r="T7" s="86">
+      <c r="T7" s="77">
         <v>2485.6999999999998</v>
       </c>
-      <c r="U7" s="87">
+      <c r="U7" s="78">
         <v>1228391</v>
       </c>
-      <c r="V7" s="85">
+      <c r="V7" s="76">
         <v>430.5</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="89">
+      <c r="A8" s="80">
         <v>2002</v>
       </c>
-      <c r="B8" s="87">
+      <c r="B8" s="78">
         <v>287973924</v>
       </c>
-      <c r="C8" s="87">
+      <c r="C8" s="78">
         <v>1423677</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="76">
         <v>494.4</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="78">
         <v>16229</v>
       </c>
-      <c r="F8" s="85">
+      <c r="F8" s="76">
         <v>5.6</v>
       </c>
-      <c r="G8" s="87"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="92">
+      <c r="G8" s="78"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="83">
         <v>95235</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="79">
         <v>33.1</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="78">
         <v>420806</v>
       </c>
-      <c r="L8" s="85">
+      <c r="L8" s="76">
         <v>146.1</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="78">
         <v>891407</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="76">
         <v>309.5</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="78">
         <v>10455277</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="77">
         <v>3630.6</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="78">
         <v>2151252</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="77">
         <v>747</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="78">
         <v>7057379</v>
       </c>
-      <c r="T8" s="86">
+      <c r="T8" s="77">
         <v>2450.6999999999998</v>
       </c>
-      <c r="U8" s="87">
+      <c r="U8" s="78">
         <v>1246646</v>
       </c>
-      <c r="V8" s="85">
+      <c r="V8" s="76">
         <v>432.9</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="89" t="s">
+      <c r="A9" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="87">
+      <c r="B9" s="78">
         <v>290788976</v>
       </c>
-      <c r="C9" s="87">
+      <c r="C9" s="78">
         <v>1383676</v>
       </c>
-      <c r="D9" s="85">
+      <c r="D9" s="76">
         <v>475.8</v>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="78">
         <v>16528</v>
       </c>
-      <c r="F9" s="85">
+      <c r="F9" s="76">
         <v>5.7</v>
       </c>
-      <c r="G9" s="87"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="92">
+      <c r="G9" s="78"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="83">
         <v>93883</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="79">
         <v>32.299999999999997</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="78">
         <v>414235</v>
       </c>
-      <c r="L9" s="85">
+      <c r="L9" s="76">
         <v>142.5</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="78">
         <v>859030</v>
       </c>
-      <c r="N9" s="85">
+      <c r="N9" s="76">
         <v>295.39999999999998</v>
       </c>
-      <c r="O9" s="87">
+      <c r="O9" s="78">
         <v>10442862</v>
       </c>
-      <c r="P9" s="86">
+      <c r="P9" s="77">
         <v>3591.2</v>
       </c>
-      <c r="Q9" s="87">
+      <c r="Q9" s="78">
         <v>2154834</v>
       </c>
-      <c r="R9" s="86">
+      <c r="R9" s="77">
         <v>741</v>
       </c>
-      <c r="S9" s="87">
+      <c r="S9" s="78">
         <v>7026802</v>
       </c>
-      <c r="T9" s="86">
+      <c r="T9" s="77">
         <v>2416.5</v>
       </c>
-      <c r="U9" s="87">
+      <c r="U9" s="78">
         <v>1261226</v>
       </c>
-      <c r="V9" s="85">
+      <c r="V9" s="76">
         <v>433.7</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="89" t="s">
+      <c r="A10" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="87">
+      <c r="B10" s="78">
         <v>293656842</v>
       </c>
-      <c r="C10" s="87">
+      <c r="C10" s="78">
         <v>1360088</v>
       </c>
-      <c r="D10" s="85">
+      <c r="D10" s="76">
         <v>463.2</v>
       </c>
-      <c r="E10" s="87">
+      <c r="E10" s="78">
         <v>16148</v>
       </c>
-      <c r="F10" s="85">
+      <c r="F10" s="76">
         <v>5.5</v>
       </c>
-      <c r="G10" s="87"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="92">
+      <c r="G10" s="78"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="83">
         <v>95089</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J10" s="79">
         <v>32.4</v>
       </c>
-      <c r="K10" s="87">
+      <c r="K10" s="78">
         <v>401470</v>
       </c>
-      <c r="L10" s="85">
+      <c r="L10" s="76">
         <v>136.69999999999999</v>
       </c>
-      <c r="M10" s="87">
+      <c r="M10" s="78">
         <v>847381</v>
       </c>
-      <c r="N10" s="85">
+      <c r="N10" s="76">
         <v>288.60000000000002</v>
       </c>
-      <c r="O10" s="87">
+      <c r="O10" s="78">
         <v>10319386</v>
       </c>
-      <c r="P10" s="86">
+      <c r="P10" s="77">
         <v>3514.1</v>
       </c>
-      <c r="Q10" s="87">
+      <c r="Q10" s="78">
         <v>2144446</v>
       </c>
-      <c r="R10" s="86">
+      <c r="R10" s="77">
         <v>730.3</v>
       </c>
-      <c r="S10" s="87">
+      <c r="S10" s="78">
         <v>6937089</v>
       </c>
-      <c r="T10" s="86">
+      <c r="T10" s="77">
         <v>2362.3000000000002</v>
       </c>
-      <c r="U10" s="87">
+      <c r="U10" s="78">
         <v>1237851</v>
       </c>
-      <c r="V10" s="85">
+      <c r="V10" s="76">
         <v>421.5</v>
       </c>
-      <c r="W10" s="59" t="s">
+      <c r="W10" s="50" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="89" t="s">
+      <c r="A11" s="80" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="87">
+      <c r="B11" s="78">
         <v>296507061</v>
       </c>
-      <c r="C11" s="87">
+      <c r="C11" s="78">
         <v>1390745</v>
       </c>
-      <c r="D11" s="85">
+      <c r="D11" s="76">
         <v>469</v>
       </c>
-      <c r="E11" s="87">
+      <c r="E11" s="78">
         <v>16740</v>
       </c>
-      <c r="F11" s="85">
+      <c r="F11" s="76">
         <v>5.6</v>
       </c>
-      <c r="G11" s="87"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="92">
+      <c r="G11" s="78"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="83">
         <v>94347</v>
       </c>
-      <c r="J11" s="88">
+      <c r="J11" s="79">
         <v>31.8</v>
       </c>
-      <c r="K11" s="87">
+      <c r="K11" s="78">
         <v>417438</v>
       </c>
-      <c r="L11" s="85">
+      <c r="L11" s="76">
         <v>140.80000000000001</v>
       </c>
-      <c r="M11" s="87">
+      <c r="M11" s="78">
         <v>862220</v>
       </c>
-      <c r="N11" s="85">
+      <c r="N11" s="76">
         <v>290.8</v>
       </c>
-      <c r="O11" s="87">
+      <c r="O11" s="78">
         <v>10174754</v>
       </c>
-      <c r="P11" s="86">
+      <c r="P11" s="77">
         <v>3431.5</v>
       </c>
-      <c r="Q11" s="87">
+      <c r="Q11" s="78">
         <v>2155448</v>
       </c>
-      <c r="R11" s="86">
+      <c r="R11" s="77">
         <v>726.9</v>
       </c>
-      <c r="S11" s="87">
+      <c r="S11" s="78">
         <v>6783447</v>
       </c>
-      <c r="T11" s="86">
+      <c r="T11" s="77">
         <v>2287.8000000000002</v>
       </c>
-      <c r="U11" s="87">
+      <c r="U11" s="78">
         <v>1235859</v>
       </c>
-      <c r="V11" s="85">
+      <c r="V11" s="76">
         <v>416.8</v>
       </c>
-      <c r="X11" s="59" t="s">
+      <c r="X11" s="50" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="87">
+      <c r="B12" s="78">
         <v>299398484</v>
       </c>
-      <c r="C12" s="87">
+      <c r="C12" s="78">
         <v>1435123</v>
       </c>
-      <c r="D12" s="85">
+      <c r="D12" s="76">
         <v>479.3</v>
       </c>
-      <c r="E12" s="87">
+      <c r="E12" s="78">
         <v>17309</v>
       </c>
-      <c r="F12" s="85">
+      <c r="F12" s="76">
         <v>5.8</v>
       </c>
-      <c r="G12" s="87" t="s">
+      <c r="G12" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="85"/>
-      <c r="I12" s="92">
+      <c r="H12" s="76"/>
+      <c r="I12" s="83">
         <v>94472</v>
       </c>
-      <c r="J12" s="88">
+      <c r="J12" s="79">
         <v>31.6</v>
       </c>
-      <c r="K12" s="87">
+      <c r="K12" s="78">
         <v>449246</v>
       </c>
-      <c r="L12" s="85">
+      <c r="L12" s="76">
         <v>150</v>
       </c>
-      <c r="M12" s="87">
+      <c r="M12" s="78">
         <v>874096</v>
       </c>
-      <c r="N12" s="85">
+      <c r="N12" s="76">
         <v>292</v>
       </c>
-      <c r="O12" s="87">
+      <c r="O12" s="78">
         <v>10019601</v>
       </c>
-      <c r="P12" s="86">
+      <c r="P12" s="77">
         <v>3346.6</v>
       </c>
-      <c r="Q12" s="87">
+      <c r="Q12" s="78">
         <v>2194993</v>
       </c>
-      <c r="R12" s="86">
+      <c r="R12" s="77">
         <v>733.1</v>
       </c>
-      <c r="S12" s="87">
+      <c r="S12" s="78">
         <v>6626363</v>
       </c>
-      <c r="T12" s="86">
+      <c r="T12" s="77">
         <v>2213.1999999999998</v>
       </c>
-      <c r="U12" s="87">
+      <c r="U12" s="78">
         <v>1198245</v>
       </c>
-      <c r="V12" s="85">
+      <c r="V12" s="76">
         <v>400.2</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="89" t="s">
+      <c r="A13" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="61">
+      <c r="B13" s="52">
         <v>301621157</v>
       </c>
-      <c r="C13" s="87">
+      <c r="C13" s="78">
         <v>1422970</v>
       </c>
-      <c r="D13" s="85">
+      <c r="D13" s="76">
         <v>471.8</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="52">
         <v>17128</v>
       </c>
-      <c r="F13" s="85">
+      <c r="F13" s="76">
         <v>5.7</v>
       </c>
-      <c r="H13" s="85"/>
-      <c r="I13" s="63">
+      <c r="H13" s="76"/>
+      <c r="I13" s="54">
         <v>92160</v>
       </c>
-      <c r="J13" s="88">
+      <c r="J13" s="79">
         <v>30.6</v>
       </c>
-      <c r="K13" s="61">
+      <c r="K13" s="52">
         <v>447324</v>
       </c>
-      <c r="L13" s="85">
+      <c r="L13" s="76">
         <v>148.30000000000001</v>
       </c>
-      <c r="M13" s="61">
+      <c r="M13" s="52">
         <v>866358</v>
       </c>
-      <c r="N13" s="85">
+      <c r="N13" s="76">
         <v>287.2</v>
       </c>
-      <c r="O13" s="87">
+      <c r="O13" s="78">
         <v>9882212</v>
       </c>
-      <c r="P13" s="86">
+      <c r="P13" s="77">
         <v>3276.4</v>
       </c>
-      <c r="Q13" s="61">
+      <c r="Q13" s="52">
         <v>2190198</v>
       </c>
-      <c r="R13" s="86">
+      <c r="R13" s="77">
         <v>726.1</v>
       </c>
-      <c r="S13" s="61">
+      <c r="S13" s="52">
         <v>6591542</v>
       </c>
-      <c r="T13" s="86">
+      <c r="T13" s="77">
         <v>2185.4</v>
       </c>
-      <c r="U13" s="61">
+      <c r="U13" s="52">
         <v>1100472</v>
       </c>
-      <c r="V13" s="85">
+      <c r="V13" s="76">
         <v>364.9</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="52">
         <v>304059724</v>
       </c>
-      <c r="C14" s="87">
+      <c r="C14" s="78">
         <v>1394461</v>
       </c>
-      <c r="D14" s="85">
+      <c r="D14" s="76">
         <v>458.6</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="52">
         <v>16465</v>
       </c>
-      <c r="F14" s="85">
+      <c r="F14" s="76">
         <v>5.4</v>
       </c>
-      <c r="H14" s="85"/>
-      <c r="I14" s="63">
+      <c r="H14" s="76"/>
+      <c r="I14" s="54">
         <v>90750</v>
       </c>
-      <c r="J14" s="88">
+      <c r="J14" s="79">
         <v>29.8</v>
       </c>
-      <c r="K14" s="61">
+      <c r="K14" s="52">
         <v>443563</v>
       </c>
-      <c r="L14" s="85">
+      <c r="L14" s="76">
         <v>145.9</v>
       </c>
-      <c r="M14" s="61">
+      <c r="M14" s="52">
         <v>843683</v>
       </c>
-      <c r="N14" s="85">
+      <c r="N14" s="76">
         <v>277.5</v>
       </c>
-      <c r="O14" s="87">
+      <c r="O14" s="78">
         <v>9774152</v>
       </c>
-      <c r="P14" s="86">
+      <c r="P14" s="77">
         <v>3214.6</v>
       </c>
-      <c r="Q14" s="61">
+      <c r="Q14" s="52">
         <v>2228887</v>
       </c>
-      <c r="R14" s="86">
+      <c r="R14" s="77">
         <v>733</v>
       </c>
-      <c r="S14" s="61">
+      <c r="S14" s="52">
         <v>6586206</v>
       </c>
-      <c r="T14" s="86">
+      <c r="T14" s="77">
         <v>2166.1</v>
       </c>
-      <c r="U14" s="61">
+      <c r="U14" s="52">
         <v>959059</v>
       </c>
-      <c r="V14" s="85">
+      <c r="V14" s="76">
         <v>315.39999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A15" s="89" t="s">
+      <c r="A15" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="61">
+      <c r="B15" s="52">
         <v>307006550</v>
       </c>
-      <c r="C15" s="87">
+      <c r="C15" s="78">
         <v>1325896</v>
       </c>
-      <c r="D15" s="85">
+      <c r="D15" s="76">
         <v>431.9</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="52">
         <v>15399</v>
       </c>
-      <c r="F15" s="85">
+      <c r="F15" s="76">
         <v>5</v>
       </c>
-      <c r="H15" s="85"/>
-      <c r="I15" s="63">
+      <c r="H15" s="76"/>
+      <c r="I15" s="54">
         <v>89241</v>
       </c>
-      <c r="J15" s="88">
+      <c r="J15" s="79">
         <v>29.1</v>
       </c>
-      <c r="K15" s="61">
+      <c r="K15" s="52">
         <v>408742</v>
       </c>
-      <c r="L15" s="85">
+      <c r="L15" s="76">
         <v>133.1</v>
       </c>
-      <c r="M15" s="61">
+      <c r="M15" s="52">
         <v>812514</v>
       </c>
-      <c r="N15" s="85">
+      <c r="N15" s="76">
         <v>264.7</v>
       </c>
-      <c r="O15" s="87">
+      <c r="O15" s="78">
         <v>9337060</v>
       </c>
-      <c r="P15" s="86">
+      <c r="P15" s="77">
         <v>3041.3</v>
       </c>
-      <c r="Q15" s="61">
+      <c r="Q15" s="52">
         <v>2203313</v>
       </c>
-      <c r="R15" s="86">
+      <c r="R15" s="77">
         <v>717.7</v>
       </c>
-      <c r="S15" s="61">
+      <c r="S15" s="52">
         <v>6338095</v>
       </c>
-      <c r="T15" s="86">
+      <c r="T15" s="77">
         <v>2064.5</v>
       </c>
-      <c r="U15" s="61">
+      <c r="U15" s="52">
         <v>795652</v>
       </c>
-      <c r="V15" s="85">
+      <c r="V15" s="76">
         <v>259.2</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="89" t="s">
+      <c r="A16" s="80" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="61">
+      <c r="B16" s="52">
         <v>309330219</v>
       </c>
-      <c r="C16" s="87">
+      <c r="C16" s="78">
         <v>1251248</v>
       </c>
-      <c r="D16" s="85">
+      <c r="D16" s="76">
         <v>404.5</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="52">
         <v>14722</v>
       </c>
-      <c r="F16" s="85">
+      <c r="F16" s="76">
         <v>4.8</v>
       </c>
-      <c r="H16" s="85"/>
-      <c r="I16" s="63">
+      <c r="H16" s="76"/>
+      <c r="I16" s="54">
         <v>85593</v>
       </c>
-      <c r="J16" s="88">
+      <c r="J16" s="79">
         <v>27.7</v>
       </c>
-      <c r="K16" s="61">
+      <c r="K16" s="52">
         <v>369089</v>
       </c>
-      <c r="L16" s="85">
+      <c r="L16" s="76">
         <v>119.3</v>
       </c>
-      <c r="M16" s="61">
+      <c r="M16" s="52">
         <v>781844</v>
       </c>
-      <c r="N16" s="85">
+      <c r="N16" s="76">
         <v>252.8</v>
       </c>
-      <c r="O16" s="87">
+      <c r="O16" s="78">
         <v>9112625</v>
       </c>
-      <c r="P16" s="86">
+      <c r="P16" s="77">
         <v>2945.9</v>
       </c>
-      <c r="Q16" s="61">
+      <c r="Q16" s="52">
         <v>2168459</v>
       </c>
-      <c r="R16" s="86">
+      <c r="R16" s="77">
         <v>701</v>
       </c>
-      <c r="S16" s="61">
+      <c r="S16" s="52">
         <v>6204601</v>
       </c>
-      <c r="T16" s="86">
+      <c r="T16" s="77">
         <v>2005.8</v>
       </c>
-      <c r="U16" s="61">
+      <c r="U16" s="52">
         <v>739565</v>
       </c>
-      <c r="V16" s="85">
+      <c r="V16" s="76">
         <v>239.1</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="61">
+      <c r="B17" s="52">
         <v>311587816</v>
       </c>
-      <c r="C17" s="87">
+      <c r="C17" s="78">
         <v>1206005</v>
       </c>
-      <c r="D17" s="85">
+      <c r="D17" s="76">
         <v>387.1</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="52">
         <v>14661</v>
       </c>
-      <c r="F17" s="85">
+      <c r="F17" s="76">
         <v>4.7</v>
       </c>
-      <c r="H17" s="85"/>
-      <c r="I17" s="63">
+      <c r="H17" s="76"/>
+      <c r="I17" s="54">
         <v>84175</v>
       </c>
-      <c r="J17" s="88">
+      <c r="J17" s="79">
         <v>27</v>
       </c>
-      <c r="K17" s="61">
+      <c r="K17" s="52">
         <v>354746</v>
       </c>
-      <c r="L17" s="85">
+      <c r="L17" s="76">
         <v>113.9</v>
       </c>
-      <c r="M17" s="61">
+      <c r="M17" s="52">
         <v>752423</v>
       </c>
-      <c r="N17" s="85">
+      <c r="N17" s="76">
         <v>241.5</v>
       </c>
-      <c r="O17" s="87">
+      <c r="O17" s="78">
         <v>9052743</v>
       </c>
-      <c r="P17" s="86">
+      <c r="P17" s="77">
         <v>2905.4</v>
       </c>
-      <c r="Q17" s="61">
+      <c r="Q17" s="52">
         <v>2185140</v>
       </c>
-      <c r="R17" s="86">
+      <c r="R17" s="77">
         <v>701.3</v>
       </c>
-      <c r="S17" s="61">
+      <c r="S17" s="52">
         <v>6151095</v>
       </c>
-      <c r="T17" s="86">
+      <c r="T17" s="77">
         <v>1974.1</v>
       </c>
-      <c r="U17" s="61">
+      <c r="U17" s="52">
         <v>716508</v>
       </c>
-      <c r="V17" s="85">
+      <c r="V17" s="76">
         <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="89" t="s">
+      <c r="A18" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="61">
+      <c r="B18" s="52">
         <v>313873685</v>
       </c>
-      <c r="C18" s="87">
+      <c r="C18" s="78">
         <v>1217057</v>
       </c>
-      <c r="D18" s="85">
+      <c r="D18" s="76">
         <v>387.8</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="52">
         <v>14856</v>
       </c>
-      <c r="F18" s="85">
+      <c r="F18" s="76">
         <v>4.7</v>
       </c>
-      <c r="H18" s="85"/>
-      <c r="I18" s="63">
+      <c r="H18" s="76"/>
+      <c r="I18" s="54">
         <v>85141</v>
       </c>
-      <c r="J18" s="88">
+      <c r="J18" s="79">
         <v>27.1</v>
       </c>
-      <c r="K18" s="61">
+      <c r="K18" s="52">
         <v>355051</v>
       </c>
-      <c r="L18" s="85">
+      <c r="L18" s="76">
         <v>113.1</v>
       </c>
-      <c r="M18" s="61">
+      <c r="M18" s="52">
         <v>762009</v>
       </c>
-      <c r="N18" s="85">
+      <c r="N18" s="76">
         <v>242.8</v>
       </c>
-      <c r="O18" s="87">
+      <c r="O18" s="78">
         <v>9001992</v>
       </c>
-      <c r="P18" s="86">
+      <c r="P18" s="77">
         <v>2868</v>
       </c>
-      <c r="Q18" s="61">
+      <c r="Q18" s="52">
         <v>2109932</v>
       </c>
-      <c r="R18" s="86">
+      <c r="R18" s="77">
         <v>672.2</v>
       </c>
-      <c r="S18" s="61">
+      <c r="S18" s="52">
         <v>6168874</v>
       </c>
-      <c r="T18" s="86">
+      <c r="T18" s="77">
         <v>1965.4</v>
       </c>
-      <c r="U18" s="61">
+      <c r="U18" s="52">
         <v>723186</v>
       </c>
-      <c r="V18" s="85">
+      <c r="V18" s="76">
         <v>230.4</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="B19" s="61">
+      <c r="B19" s="52">
         <v>316497531</v>
       </c>
-      <c r="C19" s="87">
+      <c r="C19" s="78">
         <v>1168298</v>
       </c>
-      <c r="D19" s="85">
+      <c r="D19" s="76">
         <v>369.1</v>
       </c>
-      <c r="E19" s="61">
+      <c r="E19" s="52">
         <v>14319</v>
       </c>
-      <c r="F19" s="85">
+      <c r="F19" s="76">
         <v>4.5</v>
       </c>
-      <c r="G19" s="61">
+      <c r="G19" s="52">
         <v>113695</v>
       </c>
-      <c r="H19" s="85">
+      <c r="H19" s="76">
         <v>35.9</v>
       </c>
-      <c r="I19" s="63">
+      <c r="I19" s="54">
         <v>82109</v>
       </c>
-      <c r="J19" s="88">
+      <c r="J19" s="79">
         <v>25.9</v>
       </c>
-      <c r="K19" s="61">
+      <c r="K19" s="52">
         <v>345093</v>
       </c>
-      <c r="L19" s="85">
+      <c r="L19" s="76">
         <v>109</v>
       </c>
-      <c r="M19" s="61">
+      <c r="M19" s="52">
         <v>726777</v>
       </c>
-      <c r="N19" s="85">
+      <c r="N19" s="76">
         <v>229.6</v>
       </c>
-      <c r="O19" s="87">
+      <c r="O19" s="78">
         <v>8651892</v>
       </c>
-      <c r="P19" s="86">
+      <c r="P19" s="77">
         <v>2733.6</v>
       </c>
-      <c r="Q19" s="61">
+      <c r="Q19" s="52">
         <v>1932139</v>
       </c>
-      <c r="R19" s="86">
+      <c r="R19" s="77">
         <v>610.5</v>
       </c>
-      <c r="S19" s="61">
+      <c r="S19" s="52">
         <v>6019465</v>
       </c>
-      <c r="T19" s="86">
+      <c r="T19" s="77">
         <v>1901.9</v>
       </c>
-      <c r="U19" s="61">
+      <c r="U19" s="52">
         <v>700288</v>
       </c>
-      <c r="V19" s="85">
+      <c r="V19" s="76">
         <v>221.3</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="90" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="93" t="s">
+    <row r="20" spans="1:22" s="81" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="84" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="63">
+      <c r="B20" s="54">
         <v>318907401</v>
       </c>
-      <c r="C20" s="92">
+      <c r="C20" s="83">
         <v>1153022</v>
       </c>
-      <c r="D20" s="88">
+      <c r="D20" s="79">
         <v>361.6</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E20" s="54">
         <v>14164</v>
       </c>
-      <c r="F20" s="88">
+      <c r="F20" s="79">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="54">
         <v>118027</v>
       </c>
-      <c r="H20" s="88">
+      <c r="H20" s="79">
         <v>37</v>
       </c>
-      <c r="I20" s="63">
+      <c r="I20" s="54">
         <v>84864</v>
       </c>
-      <c r="J20" s="88">
+      <c r="J20" s="79">
         <v>26.6</v>
       </c>
-      <c r="K20" s="63">
+      <c r="K20" s="54">
         <v>322905</v>
       </c>
-      <c r="L20" s="88">
+      <c r="L20" s="79">
         <v>101.3</v>
       </c>
-      <c r="M20" s="63">
+      <c r="M20" s="54">
         <v>731089</v>
       </c>
-      <c r="N20" s="88">
+      <c r="N20" s="79">
         <v>229.2</v>
       </c>
-      <c r="O20" s="92">
+      <c r="O20" s="83">
         <v>8209010</v>
       </c>
-      <c r="P20" s="91">
+      <c r="P20" s="82">
         <v>2574.1</v>
       </c>
-      <c r="Q20" s="63">
+      <c r="Q20" s="54">
         <v>1713153</v>
       </c>
-      <c r="R20" s="91">
+      <c r="R20" s="82">
         <v>537.20000000000005</v>
       </c>
-      <c r="S20" s="63">
+      <c r="S20" s="54">
         <v>5809054</v>
       </c>
-      <c r="T20" s="91">
+      <c r="T20" s="82">
         <v>1821.5</v>
       </c>
-      <c r="U20" s="63">
+      <c r="U20" s="54">
         <v>686803</v>
       </c>
-      <c r="V20" s="88">
+      <c r="V20" s="79">
         <v>215.4</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A21" s="89" t="s">
+      <c r="A21" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="61">
+      <c r="B21" s="52">
         <v>320896618</v>
       </c>
-      <c r="C21" s="87">
+      <c r="C21" s="78">
         <v>1199310</v>
       </c>
-      <c r="D21" s="85">
+      <c r="D21" s="76">
         <v>373.7</v>
       </c>
-      <c r="E21" s="61">
+      <c r="E21" s="52">
         <v>15883</v>
       </c>
-      <c r="F21" s="85">
+      <c r="F21" s="76">
         <v>4.9000000000000004</v>
       </c>
-      <c r="G21" s="61">
+      <c r="G21" s="52">
         <v>126134</v>
       </c>
-      <c r="H21" s="85">
+      <c r="H21" s="76">
         <v>39.299999999999997</v>
       </c>
-      <c r="I21" s="63">
+      <c r="I21" s="54">
         <v>91261</v>
       </c>
-      <c r="J21" s="88">
+      <c r="J21" s="79">
         <v>28.4</v>
       </c>
-      <c r="K21" s="61">
+      <c r="K21" s="52">
         <v>328109</v>
       </c>
-      <c r="L21" s="85">
+      <c r="L21" s="76">
         <v>102.2</v>
       </c>
-      <c r="M21" s="61">
+      <c r="M21" s="52">
         <v>764057</v>
       </c>
-      <c r="N21" s="85">
+      <c r="N21" s="76">
         <v>238.1</v>
       </c>
-      <c r="O21" s="87">
+      <c r="O21" s="78">
         <v>8024115</v>
       </c>
-      <c r="P21" s="86">
+      <c r="P21" s="77">
         <v>2500.5</v>
       </c>
-      <c r="Q21" s="61">
+      <c r="Q21" s="52">
         <v>1587564</v>
       </c>
-      <c r="R21" s="86">
+      <c r="R21" s="77">
         <v>494.7</v>
       </c>
-      <c r="S21" s="61">
+      <c r="S21" s="52">
         <v>5723488</v>
       </c>
-      <c r="T21" s="86">
+      <c r="T21" s="77">
         <v>1783.6</v>
       </c>
-      <c r="U21" s="61">
+      <c r="U21" s="52">
         <v>713063</v>
       </c>
-      <c r="V21" s="85">
+      <c r="V21" s="76">
         <v>222.2</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="B22" s="61">
+      <c r="A22" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" s="52">
         <v>323405935</v>
       </c>
-      <c r="C22" s="87">
+      <c r="C22" s="78">
         <v>1250162</v>
       </c>
-      <c r="D22" s="85">
+      <c r="D22" s="76">
         <v>386.6</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="52">
         <v>17413</v>
       </c>
-      <c r="F22" s="85">
+      <c r="F22" s="76">
         <v>5.4</v>
       </c>
-      <c r="G22" s="61">
+      <c r="G22" s="52">
         <v>132414</v>
       </c>
-      <c r="H22" s="85">
+      <c r="H22" s="76">
         <v>40.9</v>
       </c>
-      <c r="I22" s="63">
+      <c r="I22" s="54">
         <v>96970</v>
       </c>
-      <c r="J22" s="88">
+      <c r="J22" s="79">
         <v>30</v>
       </c>
-      <c r="K22" s="61">
+      <c r="K22" s="52">
         <v>332797</v>
       </c>
-      <c r="L22" s="85">
+      <c r="L22" s="76">
         <v>102.9</v>
       </c>
-      <c r="M22" s="61">
+      <c r="M22" s="52">
         <v>802982</v>
       </c>
-      <c r="N22" s="85">
+      <c r="N22" s="76">
         <v>248.3</v>
       </c>
-      <c r="O22" s="87">
+      <c r="O22" s="78">
         <v>7928530</v>
       </c>
-      <c r="P22" s="86">
+      <c r="P22" s="77">
         <v>2451.6</v>
       </c>
-      <c r="Q22" s="61">
+      <c r="Q22" s="52">
         <v>1516405</v>
       </c>
-      <c r="R22" s="86">
+      <c r="R22" s="77">
         <v>468.9</v>
       </c>
-      <c r="S22" s="61">
+      <c r="S22" s="52">
         <v>5644835</v>
       </c>
-      <c r="T22" s="86">
+      <c r="T22" s="77">
         <v>1745.4</v>
       </c>
-      <c r="U22" s="61">
+      <c r="U22" s="52">
         <v>767290</v>
       </c>
-      <c r="V22" s="85">
+      <c r="V22" s="76">
         <v>237.3</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="89" t="s">
+      <c r="A23" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="61">
+      <c r="B23" s="52">
         <v>325147121</v>
       </c>
-      <c r="C23" s="87">
+      <c r="C23" s="78">
         <v>1247917</v>
       </c>
-      <c r="D23" s="85">
+      <c r="D23" s="76">
         <v>383.8</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="52">
         <v>17294</v>
       </c>
-      <c r="F23" s="85">
+      <c r="F23" s="76">
         <v>5.3</v>
       </c>
-      <c r="G23" s="61">
+      <c r="G23" s="52">
         <v>135666</v>
       </c>
-      <c r="H23" s="85">
+      <c r="H23" s="76">
         <v>41.7</v>
       </c>
-      <c r="I23" s="63">
+      <c r="I23" s="54">
         <v>99708</v>
       </c>
-      <c r="J23" s="88">
+      <c r="J23" s="79">
         <v>30.7</v>
       </c>
-      <c r="K23" s="61">
+      <c r="K23" s="52">
         <v>320596</v>
       </c>
-      <c r="L23" s="85">
+      <c r="L23" s="76">
         <v>98.6</v>
       </c>
-      <c r="M23" s="61">
+      <c r="M23" s="52">
         <v>810319</v>
       </c>
-      <c r="N23" s="85">
+      <c r="N23" s="76">
         <v>249.2</v>
       </c>
-      <c r="O23" s="87">
+      <c r="O23" s="78">
         <v>7682988</v>
       </c>
-      <c r="P23" s="86">
+      <c r="P23" s="77">
         <v>2362.9</v>
       </c>
-      <c r="Q23" s="61">
+      <c r="Q23" s="52">
         <v>1397045</v>
       </c>
-      <c r="R23" s="86">
+      <c r="R23" s="77">
         <v>429.7</v>
       </c>
-      <c r="S23" s="61">
+      <c r="S23" s="52">
         <v>5513000</v>
       </c>
-      <c r="T23" s="86">
+      <c r="T23" s="77">
         <v>1695.5</v>
       </c>
-      <c r="U23" s="61">
+      <c r="U23" s="52">
         <v>772943</v>
       </c>
-      <c r="V23" s="85">
+      <c r="V23" s="76">
         <v>237.7</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="61">
+      <c r="B24" s="52">
         <v>327167434</v>
       </c>
-      <c r="C24" s="87">
+      <c r="C24" s="78">
         <v>1206836</v>
       </c>
-      <c r="D24" s="85">
+      <c r="D24" s="76">
         <v>368.9</v>
       </c>
-      <c r="E24" s="61">
+      <c r="E24" s="52">
         <v>16214</v>
       </c>
-      <c r="F24" s="85">
+      <c r="F24" s="76">
         <v>5</v>
       </c>
-      <c r="G24" s="61">
+      <c r="G24" s="52">
         <v>139380</v>
       </c>
-      <c r="H24" s="85">
+      <c r="H24" s="76">
         <v>42.6</v>
       </c>
-      <c r="I24" s="63">
+      <c r="I24" s="54">
         <v>101151</v>
       </c>
-      <c r="J24" s="88">
+      <c r="J24" s="79">
         <v>30.9</v>
       </c>
-      <c r="K24" s="61">
+      <c r="K24" s="52">
         <v>282061</v>
       </c>
-      <c r="L24" s="85">
+      <c r="L24" s="76">
         <v>86.2</v>
       </c>
-      <c r="M24" s="61">
+      <c r="M24" s="52">
         <v>807410</v>
       </c>
-      <c r="N24" s="85">
+      <c r="N24" s="76">
         <v>246.8</v>
       </c>
-      <c r="O24" s="87">
+      <c r="O24" s="78">
         <v>7196045</v>
       </c>
-      <c r="P24" s="86">
+      <c r="P24" s="77">
         <v>2199.5</v>
       </c>
-      <c r="Q24" s="61">
+      <c r="Q24" s="52">
         <v>1230149</v>
       </c>
-      <c r="R24" s="86">
+      <c r="R24" s="77">
         <v>376</v>
       </c>
-      <c r="S24" s="61">
+      <c r="S24" s="52">
         <v>5217055</v>
       </c>
-      <c r="T24" s="86">
+      <c r="T24" s="77">
         <v>1594.6</v>
       </c>
-      <c r="U24" s="61">
+      <c r="U24" s="52">
         <v>748841</v>
       </c>
-      <c r="V24" s="85">
+      <c r="V24" s="76">
         <v>228.9</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="67" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="84" t="s">
+    <row r="25" spans="1:22" s="58" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="82"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="82"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="82"/>
-      <c r="H25" s="82"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="82"/>
-      <c r="L25" s="82"/>
-      <c r="M25" s="82"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="81"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="81"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="81"/>
-      <c r="T25" s="81"/>
-      <c r="U25" s="81"/>
-      <c r="V25" s="81"/>
-    </row>
-    <row r="26" spans="1:22" s="67" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="80" t="s">
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="74"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="72"/>
+      <c r="V25" s="72"/>
+    </row>
+    <row r="26" spans="1:22" s="58" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="71" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="8"/>
@@ -10672,81 +10726,81 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="75"/>
-    </row>
-    <row r="27" spans="1:22" s="67" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="78" t="s">
+      <c r="Q26" s="66"/>
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
+      <c r="V26" s="66"/>
+    </row>
+    <row r="27" spans="1:22" s="58" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
-      <c r="N27" s="79" t="s">
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="O27" s="75" t="s">
+      <c r="O27" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
-      <c r="T27" s="75"/>
-      <c r="U27" s="75"/>
-      <c r="V27" s="75"/>
-    </row>
-    <row r="28" spans="1:22" s="67" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="78" t="s">
+      <c r="P27" s="66"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="66"/>
+      <c r="S27" s="66"/>
+      <c r="T27" s="66"/>
+      <c r="U27" s="66"/>
+      <c r="V27" s="66"/>
+    </row>
+    <row r="28" spans="1:22" s="58" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
       <c r="N28" s="8"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="75" t="s">
+      <c r="O28" s="66"/>
+      <c r="P28" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="Q28" s="75"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="75"/>
-      <c r="T28" s="75"/>
-      <c r="U28" s="75"/>
-      <c r="V28" s="75"/>
-    </row>
-    <row r="29" spans="1:22" s="66" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="73" t="s">
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="66"/>
+      <c r="U28" s="66"/>
+      <c r="V28" s="66"/>
+    </row>
+    <row r="29" spans="1:22" s="57" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="64" t="s">
         <v>93</v>
       </c>
       <c r="B29" s="8"/>
@@ -10756,71 +10810,71 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="69"/>
-      <c r="Q29" s="70" t="s">
+      <c r="M29" s="61"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="61"/>
+      <c r="P29" s="60"/>
+      <c r="Q29" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="R29" s="69"/>
-      <c r="S29" s="70"/>
-      <c r="T29" s="69"/>
-      <c r="U29" s="70"/>
-      <c r="V29" s="69"/>
-    </row>
-    <row r="30" spans="1:22" s="66" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="73" t="s">
+      <c r="R29" s="60"/>
+      <c r="S29" s="61"/>
+      <c r="T29" s="60"/>
+      <c r="U29" s="61"/>
+      <c r="V29" s="60"/>
+    </row>
+    <row r="30" spans="1:22" s="57" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="71"/>
-      <c r="P30" s="69" t="s">
+      <c r="B30" s="62"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="Q30" s="70"/>
-      <c r="R30" s="69"/>
-      <c r="S30" s="70"/>
-      <c r="T30" s="69"/>
-      <c r="U30" s="70"/>
-      <c r="V30" s="69"/>
-    </row>
-    <row r="31" spans="1:22" s="66" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="66" t="s">
+      <c r="Q30" s="61"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="61"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="61"/>
+      <c r="V30" s="60"/>
+    </row>
+    <row r="31" spans="1:22" s="57" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="67"/>
-      <c r="Q31" s="67"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
       <c r="R31" s="8"/>
       <c r="S31" s="8"/>
       <c r="T31" s="8"/>
@@ -10828,44 +10882,44 @@
       <c r="V31" s="8"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B32" s="65"/>
-      <c r="C32" s="64"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="55"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="65"/>
-      <c r="C33" s="64"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="55"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B34" s="65"/>
-      <c r="C34" s="64"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="55"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="65"/>
-      <c r="C35" s="64"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="55"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B36" s="65"/>
-      <c r="C36" s="64"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="55"/>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B37" s="65"/>
-      <c r="C37" s="64"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="55"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B38" s="65"/>
-      <c r="C38" s="64"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="55"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B39" s="65"/>
-      <c r="C39" s="64"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="55"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B40" s="65"/>
-      <c r="C40" s="64"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="55"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B41" s="65"/>
-      <c r="C41" s="64"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="55"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
